--- a/data/measurements_2026-10-18.xlsx
+++ b/data/measurements_2026-10-18.xlsx
@@ -37,7 +37,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Day 0 = night of Oct 12, 2026. The pre-registered measurement day is Day 7 (Oct 19). Change this if you measure on a different day.</t>
+          <t xml:space="preserve">Day 0 = night of Oct 12, 2026. The final measurement was taken on the evening of Oct 18 (Day 6) instead of the pre-registered Day 7; see Amendment 1 in prereg.md.</t>
         </r>
       </text>
     </comment>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="76">
   <si>
     <t xml:space="preserve">Greywater Germination Experiment: Measurement Record</t>
   </si>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">2.</t>
   </si>
   <si>
-    <t xml:space="preserve">In the Seedlings sheet, enter one row per seed: germinated (1 or 0), hypocotyl length in mm, a flag, and the photo file name.</t>
+    <t xml:space="preserve">In the Seedlings sheet, enter one row per seed: germinated (1 or 0), hypocotyl length in mm, and a flag. photo_file is optional (record photos only).</t>
   </si>
   <si>
     <t xml:space="preserve">3.</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">Hypocotyl length</t>
   </si>
   <si>
-    <t xml:space="preserve">From the root-shoot junction (where root hairs stop) to the base of the seed leaves, traced along the curve in ImageJ/Fiji, in mm.</t>
+    <t xml:space="preserve">From the root-shoot junction (where root hairs stop) to the base of the seed leaves, measured along the curve by hand with a flexible tape measure, in mm, after lifting the whole towel out and laying it flat.</t>
   </si>
   <si>
     <t xml:space="preserve">Ungerminated seed</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">Upright seedling</t>
   </si>
   <si>
-    <t xml:space="preserve">Lay it flat gently before the photo; flag = upright_flattened.</t>
+    <t xml:space="preserve">Lay it flat gently before measuring; flag = upright_flattened.</t>
   </si>
   <si>
     <t xml:space="preserve">Tangled seedlings</t>
@@ -275,9 +275,6 @@
     <t xml:space="preserve">upright_flattened</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-18_id07.jpg</t>
-  </si>
-  <si>
     <t xml:space="preserve">example only</t>
   </si>
   <si>
@@ -323,22 +320,40 @@
     <t xml:space="preserve">ALL</t>
   </si>
   <si>
+    <t xml:space="preserve">plant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 0: 10 seeds per container; 3 mL of assigned solution. Confirm time.</t>
+  </si>
+  <si>
     <t xml:space="preserve">observe</t>
   </si>
   <si>
-    <t xml:space="preserve">Seedlings touching lids (Day 6). Confirm time.</t>
+    <t xml:space="preserve">Day 6: cucumber seedlings touching lids; roots grown into towels.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">measure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 6: towel lifted out and laid flat; hypocotyls measured by hand with tape measure; no photos. No watering, checks or photos on Days 1-5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 6, after measuring: each container given 3 mL of its own solution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lids_on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 6: lids put back on after measuring.</t>
   </si>
   <si>
     <t xml:space="preserve">photo</t>
   </si>
   <si>
-    <t xml:space="preserve">As-is photos of all 48 containers, before removing lids. Confirm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remove_lids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All 48 lids removed. Confirm time.</t>
+    <t xml:space="preserve">Day 7: record photos of all 48 containers (not used for measurement).</t>
   </si>
 </sst>
 </file>
@@ -916,7 +931,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -1040,16 +1055,14 @@
         <v>1</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="J27" s="6"/>
+      <c r="K27" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1088,13 +1101,13 @@
         <v>38</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1390,7 +1403,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -1402,7 +1415,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -1414,7 +1427,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -1426,7 +1439,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -1438,7 +1451,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -1450,7 +1463,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
@@ -1462,7 +1475,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -1474,7 +1487,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
@@ -1486,7 +1499,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -1498,7 +1511,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
@@ -1510,7 +1523,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
@@ -1522,7 +1535,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -1534,7 +1547,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -1546,7 +1559,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
@@ -1558,7 +1571,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -1570,7 +1583,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
@@ -1582,7 +1595,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
@@ -1594,7 +1607,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
@@ -1606,7 +1619,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
@@ -1618,7 +1631,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
@@ -1630,7 +1643,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
@@ -1642,7 +1655,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
@@ -1654,7 +1667,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
@@ -1666,7 +1679,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
@@ -15724,19 +15737,19 @@
         <v>38</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>58</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17358,22 +17371,22 @@
         <v>34</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>36</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>38</v>
       </c>
       <c r="F1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>44</v>
@@ -17381,20 +17394,22 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="n">
-        <v>46313</v>
+        <v>46307</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>65</v>
-      </c>
       <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
+      <c r="F2" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17403,16 +17418,16 @@
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
       <c r="H3" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17421,47 +17436,73 @@
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
       <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
+      <c r="F5" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="H5" s="9" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14"/>
+      <c r="A6" s="14" t="n">
+        <v>46313</v>
+      </c>
       <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
+      <c r="C6" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="H6" s="9" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14"/>
+      <c r="A7" s="14" t="n">
+        <v>46314</v>
+      </c>
       <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
+      <c r="C7" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>74</v>
+      </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="H7" s="9" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14"/>
